--- a/workpaper_templates/WP14_Wages_Payroll_Reconciliation.xlsx
+++ b/workpaper_templates/WP14_Wages_Payroll_Reconciliation.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +59,17 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +104,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -196,13 +241,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -695,15 +757,21 @@
           <t>Q1 Jul–Sep</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="11">
+        <f>B6-C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="12">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -711,15 +779,21 @@
           <t>Q2 Oct–Dec</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="11">
+        <f>B7-C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="12">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -727,15 +801,21 @@
           <t>Q3 Jan–Mar</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="11">
+        <f>B8-C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="12">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -743,31 +823,55 @@
           <t>Q4 Apr–Jun</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="11">
+        <f>B9-C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="12">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="B10" s="14">
+        <f>SUM(B6:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="14">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="14">
+        <f>SUM(D6:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>SUM(G6:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11" ht="6" customHeight="1">
       <c r="A11" s="5" t="n"/>
@@ -826,15 +930,18 @@
           <t>Gross wages</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="12">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="16" t="inlineStr"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -842,15 +949,18 @@
           <t>PAYG withholding</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="12">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="16" t="inlineStr"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -858,15 +968,18 @@
           <t>Superannuation</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="12">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="16" t="inlineStr"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -874,15 +987,18 @@
           <t>Reportable fringe benefits</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr"/>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="12">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="16" t="inlineStr"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -890,15 +1006,18 @@
           <t>Reportable employer super</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr"/>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr"/>
+      <c r="D18" s="12">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="16" t="inlineStr"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1">
       <c r="A19" s="5" t="n"/>
@@ -965,15 +1084,21 @@
           <t>Q1 Jul–Sep</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr"/>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="17" t="inlineStr"/>
+      <c r="D22" s="11">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="12">
+        <f>D22-E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="16" t="inlineStr"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -981,15 +1106,21 @@
           <t>Q2 Oct–Dec</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr"/>
-      <c r="C23" s="9" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr"/>
+      <c r="D23" s="11">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="12">
+        <f>D23-E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="16" t="inlineStr"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -997,15 +1128,21 @@
           <t>Q3 Jan–Mar</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr"/>
+      <c r="D24" s="11">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="12">
+        <f>D24-E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="16" t="inlineStr"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -1013,15 +1150,21 @@
           <t>Q4 Apr–Jun</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="B25" s="10" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr"/>
+      <c r="D25" s="11">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="12">
+        <f>D25-E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="16" t="inlineStr"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
     </row>
     <row r="26" ht="6" customHeight="1">
       <c r="A26" s="5" t="n"/>
@@ -1043,52 +1186,52 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="11" t="n"/>
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="19" t="n"/>
+      <c r="I28" s="19" t="n"/>
+      <c r="J28" s="20" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="11" t="n"/>
+      <c r="A29" s="18" t="inlineStr"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19" t="n"/>
+      <c r="J29" s="20" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="11" t="n"/>
+      <c r="A30" s="18" t="inlineStr"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
+      <c r="J30" s="20" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="11" t="n"/>
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="20" t="n"/>
     </row>
     <row r="32" ht="6" customHeight="1">
       <c r="A32" s="5" t="n"/>
@@ -1110,84 +1253,84 @@
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>{{preparer}}</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>{{date_prepared}}</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>{{reviewer}}</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>{{date_reviewed}}</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
+      <c r="B36" s="24" t="inlineStr"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1209,6 +1352,30 @@
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
+  <conditionalFormatting sqref="G6:G10">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:D18">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F25">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>